--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124311565</v>
+        <v>124311397</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561474</v>
+        <v>561425</v>
       </c>
       <c r="R2" t="n">
-        <v>6397726</v>
+        <v>6397700</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311750</v>
+        <v>124311718</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561517</v>
+        <v>561494</v>
       </c>
       <c r="R3" t="n">
-        <v>6397650</v>
+        <v>6397696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311500</v>
+        <v>124311630</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561472</v>
+        <v>561506</v>
       </c>
       <c r="R4" t="n">
-        <v>6397728</v>
+        <v>6397695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124313669</v>
+        <v>124311750</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561558</v>
+        <v>561517</v>
       </c>
       <c r="R5" t="n">
-        <v>6397704</v>
+        <v>6397650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311285</v>
+        <v>124313606</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561408</v>
+        <v>561566</v>
       </c>
       <c r="R6" t="n">
-        <v>6397661</v>
+        <v>6397691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313836</v>
+        <v>124313772</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1242,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561563</v>
+        <v>561604</v>
       </c>
       <c r="R7" t="n">
-        <v>6397866</v>
+        <v>6397797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124311790</v>
+        <v>124311565</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,35 +1356,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561516</v>
+        <v>561474</v>
       </c>
       <c r="R8" t="n">
-        <v>6397663</v>
+        <v>6397726</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124313702</v>
+        <v>124311790</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561582</v>
+        <v>561516</v>
       </c>
       <c r="R9" t="n">
-        <v>6397716</v>
+        <v>6397663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311311</v>
+        <v>124313669</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1614,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561426</v>
+        <v>561558</v>
       </c>
       <c r="R10" t="n">
-        <v>6397656</v>
+        <v>6397704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124313606</v>
+        <v>124313812</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1725,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561566</v>
+        <v>561599</v>
       </c>
       <c r="R11" t="n">
-        <v>6397691</v>
+        <v>6397835</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311630</v>
+        <v>124311285</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1836,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561506</v>
+        <v>561408</v>
       </c>
       <c r="R12" t="n">
-        <v>6397695</v>
+        <v>6397661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124313812</v>
+        <v>124311500</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1947,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561599</v>
+        <v>561472</v>
       </c>
       <c r="R13" t="n">
-        <v>6397835</v>
+        <v>6397728</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311718</v>
+        <v>124313836</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2058,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561494</v>
+        <v>561563</v>
       </c>
       <c r="R14" t="n">
-        <v>6397696</v>
+        <v>6397866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311366</v>
+        <v>124313702</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2169,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561431</v>
+        <v>561582</v>
       </c>
       <c r="R15" t="n">
-        <v>6397666</v>
+        <v>6397716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124313772</v>
+        <v>124311311</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,38 +2247,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561604</v>
+        <v>561426</v>
       </c>
       <c r="R16" t="n">
-        <v>6397797</v>
+        <v>6397656</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311397</v>
+        <v>124311366</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561425</v>
+        <v>561431</v>
       </c>
       <c r="R18" t="n">
-        <v>6397700</v>
+        <v>6397666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370264</v>
+        <v>124358796</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,49 +2580,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561577</v>
+        <v>561533</v>
       </c>
       <c r="R19" t="n">
-        <v>6397687</v>
+        <v>6397592</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,12 +2647,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,29 +2661,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124359633</v>
+        <v>124370264</v>
       </c>
       <c r="B20" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,41 +2691,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561533</v>
+        <v>561577</v>
       </c>
       <c r="R20" t="n">
-        <v>6397592</v>
+        <v>6397687</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2749,12 +2757,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,28 +2771,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370146</v>
+        <v>124359731</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,49 +2802,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561565</v>
+        <v>561466</v>
       </c>
       <c r="R21" t="n">
-        <v>6397707</v>
+        <v>6397610</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,29 +2883,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124358796</v>
+        <v>124370108</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,50 +2913,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561533</v>
+        <v>561549</v>
       </c>
       <c r="R22" t="n">
-        <v>6397592</v>
+        <v>6397690</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,28 +2993,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124358564</v>
+        <v>124356739</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,25 +3024,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3043,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561553</v>
+        <v>561558</v>
       </c>
       <c r="R23" t="n">
-        <v>6397632</v>
+        <v>6397751</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3105,7 +3114,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370087</v>
+        <v>124370368</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3153,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561547</v>
+        <v>561525</v>
       </c>
       <c r="R24" t="n">
-        <v>6397746</v>
+        <v>6397602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3327,7 +3336,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124358517</v>
+        <v>124370087</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3361,19 +3370,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561553</v>
+        <v>561547</v>
       </c>
       <c r="R26" t="n">
-        <v>6397632</v>
+        <v>6397746</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3411,25 +3428,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124356739</v>
+        <v>124370066</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3463,19 +3481,27 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561558</v>
+        <v>561539</v>
       </c>
       <c r="R27" t="n">
-        <v>6397751</v>
+        <v>6397729</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3513,25 +3539,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370348</v>
+        <v>124370019</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3579,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561531</v>
+        <v>561503</v>
       </c>
       <c r="R28" t="n">
-        <v>6397636</v>
+        <v>6397727</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370108</v>
+        <v>124369689</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3654,35 +3681,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3690,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561549</v>
+        <v>561476</v>
       </c>
       <c r="R29" t="n">
-        <v>6397690</v>
+        <v>6397662</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3720,12 +3751,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3734,7 +3765,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3746,17 +3776,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369824</v>
+        <v>124358564</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3765,49 +3795,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561459</v>
+        <v>561553</v>
       </c>
       <c r="R30" t="n">
-        <v>6397783</v>
+        <v>6397632</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,11 +3859,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,19 +3873,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370368</v>
+        <v>124368692</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3901,28 +3918,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561525</v>
+        <v>561429</v>
       </c>
       <c r="R31" t="n">
-        <v>6397602</v>
+        <v>6397658</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3967,19 +3984,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124368692</v>
+        <v>124370348</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4012,28 +4029,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561429</v>
+        <v>561531</v>
       </c>
       <c r="R32" t="n">
-        <v>6397658</v>
+        <v>6397636</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4078,22 +4095,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124359731</v>
+        <v>124369824</v>
       </c>
       <c r="B33" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4106,46 +4123,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561466</v>
+        <v>561459</v>
       </c>
       <c r="R33" t="n">
-        <v>6397610</v>
+        <v>6397783</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4175,6 +4191,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4189,19 +4210,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124370019</v>
+        <v>124358517</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4235,27 +4256,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561503</v>
+        <v>561553</v>
       </c>
       <c r="R34" t="n">
-        <v>6397727</v>
+        <v>6397632</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4293,29 +4306,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124369689</v>
+        <v>124370329</v>
       </c>
       <c r="B35" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4324,39 +4336,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4364,13 +4372,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561476</v>
+        <v>561575</v>
       </c>
       <c r="R35" t="n">
-        <v>6397662</v>
+        <v>6397630</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4394,12 +4402,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4408,6 +4416,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4419,17 +4428,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370066</v>
+        <v>124359633</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4438,49 +4447,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561539</v>
+        <v>561533</v>
       </c>
       <c r="R36" t="n">
-        <v>6397729</v>
+        <v>6397592</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4518,26 +4519,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370329</v>
+        <v>124370146</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561575</v>
+        <v>561565</v>
       </c>
       <c r="R37" t="n">
-        <v>6397630</v>
+        <v>6397707</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124311397</v>
+        <v>124311718</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561425</v>
+        <v>561494</v>
       </c>
       <c r="R2" t="n">
-        <v>6397700</v>
+        <v>6397696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311718</v>
+        <v>124313702</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561494</v>
+        <v>561582</v>
       </c>
       <c r="R3" t="n">
-        <v>6397696</v>
+        <v>6397716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311630</v>
+        <v>124311790</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561506</v>
+        <v>561516</v>
       </c>
       <c r="R4" t="n">
-        <v>6397695</v>
+        <v>6397663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311750</v>
+        <v>124313606</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561517</v>
+        <v>561566</v>
       </c>
       <c r="R5" t="n">
-        <v>6397650</v>
+        <v>6397691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124313606</v>
+        <v>124313669</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561566</v>
+        <v>561558</v>
       </c>
       <c r="R6" t="n">
-        <v>6397691</v>
+        <v>6397704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313772</v>
+        <v>124311500</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,38 +1242,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561604</v>
+        <v>561472</v>
       </c>
       <c r="R7" t="n">
-        <v>6397797</v>
+        <v>6397728</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124311565</v>
+        <v>124311366</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1353,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1389,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561474</v>
+        <v>561431</v>
       </c>
       <c r="R8" t="n">
-        <v>6397726</v>
+        <v>6397666</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124311790</v>
+        <v>124313836</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1506,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561516</v>
+        <v>561563</v>
       </c>
       <c r="R9" t="n">
-        <v>6397663</v>
+        <v>6397866</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124313669</v>
+        <v>124311750</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1617,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561558</v>
+        <v>561517</v>
       </c>
       <c r="R10" t="n">
-        <v>6397704</v>
+        <v>6397650</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124313812</v>
+        <v>124313772</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,35 +1686,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561599</v>
+        <v>561604</v>
       </c>
       <c r="R11" t="n">
-        <v>6397835</v>
+        <v>6397797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311285</v>
+        <v>124311630</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1839,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561408</v>
+        <v>561506</v>
       </c>
       <c r="R12" t="n">
-        <v>6397661</v>
+        <v>6397695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124311500</v>
+        <v>124311285</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1950,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561472</v>
+        <v>561408</v>
       </c>
       <c r="R13" t="n">
-        <v>6397728</v>
+        <v>6397661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124313836</v>
+        <v>124311565</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2022,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561563</v>
+        <v>561474</v>
       </c>
       <c r="R14" t="n">
-        <v>6397866</v>
+        <v>6397726</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124313702</v>
+        <v>124311397</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561582</v>
+        <v>561425</v>
       </c>
       <c r="R15" t="n">
-        <v>6397716</v>
+        <v>6397700</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124311342</v>
+        <v>124313812</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561426</v>
+        <v>561599</v>
       </c>
       <c r="R17" t="n">
-        <v>6397672</v>
+        <v>6397835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311366</v>
+        <v>124311342</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561431</v>
+        <v>561426</v>
       </c>
       <c r="R18" t="n">
-        <v>6397666</v>
+        <v>6397672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124358796</v>
+        <v>124370368</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,50 +2580,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561533</v>
+        <v>561525</v>
       </c>
       <c r="R19" t="n">
-        <v>6397592</v>
+        <v>6397602</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2661,25 +2660,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124370264</v>
+        <v>124356739</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2713,27 +2713,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561577</v>
+        <v>561558</v>
       </c>
       <c r="R20" t="n">
-        <v>6397687</v>
+        <v>6397751</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2757,12 +2749,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2771,29 +2763,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124359731</v>
+        <v>124370108</v>
       </c>
       <c r="B21" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,50 +2793,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561466</v>
+        <v>561549</v>
       </c>
       <c r="R21" t="n">
-        <v>6397610</v>
+        <v>6397690</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2883,28 +2873,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124370108</v>
+        <v>124358564</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,49 +2904,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561549</v>
+        <v>561553</v>
       </c>
       <c r="R22" t="n">
-        <v>6397690</v>
+        <v>6397632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2993,29 +2976,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124356739</v>
+        <v>124369824</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,41 +3006,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561558</v>
+        <v>561459</v>
       </c>
       <c r="R23" t="n">
-        <v>6397751</v>
+        <v>6397783</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,6 +3078,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,19 +3097,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370368</v>
+        <v>124368692</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3147,28 +3142,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561525</v>
+        <v>561429</v>
       </c>
       <c r="R24" t="n">
-        <v>6397602</v>
+        <v>6397658</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3213,19 +3208,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369964</v>
+        <v>124370264</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561506</v>
+        <v>561577</v>
       </c>
       <c r="R25" t="n">
-        <v>6397736</v>
+        <v>6397687</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,12 +3298,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3336,10 +3331,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370087</v>
+        <v>124359731</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3348,49 +3343,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561547</v>
+        <v>561466</v>
       </c>
       <c r="R26" t="n">
-        <v>6397746</v>
+        <v>6397610</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3428,29 +3424,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370066</v>
+        <v>124369689</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3459,35 +3454,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3495,13 +3494,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561539</v>
+        <v>561476</v>
       </c>
       <c r="R27" t="n">
-        <v>6397729</v>
+        <v>6397662</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,12 +3524,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3539,7 +3538,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3551,14 +3549,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370019</v>
+        <v>124370087</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3606,10 +3604,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561503</v>
+        <v>561547</v>
       </c>
       <c r="R28" t="n">
-        <v>6397727</v>
+        <v>6397746</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,10 +3667,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124369689</v>
+        <v>124358796</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,21 +3683,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3707,27 +3705,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561476</v>
+        <v>561533</v>
       </c>
       <c r="R29" t="n">
-        <v>6397662</v>
+        <v>6397592</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3751,12 +3746,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3771,22 +3766,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124358564</v>
+        <v>124370019</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,41 +3790,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561553</v>
+        <v>561503</v>
       </c>
       <c r="R30" t="n">
-        <v>6397632</v>
+        <v>6397727</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3867,25 +3870,26 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124368692</v>
+        <v>124370146</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3918,28 +3922,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561429</v>
+        <v>561565</v>
       </c>
       <c r="R31" t="n">
-        <v>6397658</v>
+        <v>6397707</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3984,19 +3988,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370348</v>
+        <v>124370329</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4044,10 +4048,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561531</v>
+        <v>561575</v>
       </c>
       <c r="R32" t="n">
-        <v>6397636</v>
+        <v>6397630</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4100,17 +4104,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124369824</v>
+        <v>124369964</v>
       </c>
       <c r="B33" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4119,35 +4123,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4155,10 +4159,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561459</v>
+        <v>561506</v>
       </c>
       <c r="R33" t="n">
-        <v>6397783</v>
+        <v>6397736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4193,17 +4197,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124370329</v>
+        <v>124370066</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561575</v>
+        <v>561539</v>
       </c>
       <c r="R35" t="n">
-        <v>6397630</v>
+        <v>6397729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370146</v>
+        <v>124370348</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561565</v>
+        <v>561531</v>
       </c>
       <c r="R37" t="n">
-        <v>6397707</v>
+        <v>6397636</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124311718</v>
+        <v>124313836</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561494</v>
+        <v>561563</v>
       </c>
       <c r="R2" t="n">
-        <v>6397696</v>
+        <v>6397866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124313702</v>
+        <v>124311565</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561582</v>
+        <v>561474</v>
       </c>
       <c r="R3" t="n">
-        <v>6397716</v>
+        <v>6397726</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311790</v>
+        <v>124311342</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561516</v>
+        <v>561426</v>
       </c>
       <c r="R4" t="n">
-        <v>6397663</v>
+        <v>6397672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124313606</v>
+        <v>124311630</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561566</v>
+        <v>561506</v>
       </c>
       <c r="R5" t="n">
-        <v>6397691</v>
+        <v>6397695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124313669</v>
+        <v>124311718</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561558</v>
+        <v>561494</v>
       </c>
       <c r="R6" t="n">
-        <v>6397704</v>
+        <v>6397696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124311500</v>
+        <v>124313606</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561472</v>
+        <v>561566</v>
       </c>
       <c r="R7" t="n">
-        <v>6397728</v>
+        <v>6397691</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124311366</v>
+        <v>124313669</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561431</v>
+        <v>561558</v>
       </c>
       <c r="R8" t="n">
-        <v>6397666</v>
+        <v>6397704</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124313836</v>
+        <v>124311750</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561563</v>
+        <v>561517</v>
       </c>
       <c r="R9" t="n">
-        <v>6397866</v>
+        <v>6397650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311750</v>
+        <v>124311790</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561517</v>
+        <v>561516</v>
       </c>
       <c r="R10" t="n">
-        <v>6397650</v>
+        <v>6397663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124313772</v>
+        <v>124311311</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,38 +1689,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561604</v>
+        <v>561426</v>
       </c>
       <c r="R11" t="n">
-        <v>6397797</v>
+        <v>6397656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311630</v>
+        <v>124311500</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561506</v>
+        <v>561472</v>
       </c>
       <c r="R12" t="n">
-        <v>6397695</v>
+        <v>6397728</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124311285</v>
+        <v>124313772</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,35 +1911,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1947,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561408</v>
+        <v>561604</v>
       </c>
       <c r="R13" t="n">
-        <v>6397661</v>
+        <v>6397797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311565</v>
+        <v>124311285</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,39 +2025,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,13 +2061,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561474</v>
+        <v>561408</v>
       </c>
       <c r="R14" t="n">
-        <v>6397726</v>
+        <v>6397661</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,6 +2105,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311397</v>
+        <v>124311366</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561425</v>
+        <v>561431</v>
       </c>
       <c r="R15" t="n">
-        <v>6397700</v>
+        <v>6397666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311311</v>
+        <v>124311397</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561426</v>
+        <v>561425</v>
       </c>
       <c r="R16" t="n">
-        <v>6397656</v>
+        <v>6397700</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311342</v>
+        <v>124313702</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561426</v>
+        <v>561582</v>
       </c>
       <c r="R18" t="n">
-        <v>6397672</v>
+        <v>6397716</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370368</v>
+        <v>124356739</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2602,27 +2602,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561525</v>
+        <v>561558</v>
       </c>
       <c r="R19" t="n">
-        <v>6397602</v>
+        <v>6397751</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,26 +2652,25 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124356739</v>
+        <v>124370066</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2713,19 +2704,27 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561558</v>
+        <v>561539</v>
       </c>
       <c r="R20" t="n">
-        <v>6397751</v>
+        <v>6397729</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,28 +2762,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370108</v>
+        <v>124369824</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,35 +2793,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561549</v>
+        <v>561459</v>
       </c>
       <c r="R21" t="n">
-        <v>6397690</v>
+        <v>6397783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,13 +2867,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2885,17 +2889,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124358564</v>
+        <v>124368692</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,38 +2908,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561553</v>
+        <v>561429</v>
       </c>
       <c r="R22" t="n">
-        <v>6397632</v>
+        <v>6397658</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2976,6 +2988,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +3000,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369824</v>
+        <v>124370329</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,35 +3019,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3042,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561459</v>
+        <v>561575</v>
       </c>
       <c r="R23" t="n">
-        <v>6397783</v>
+        <v>6397630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,17 +3093,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3102,14 +3111,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124368692</v>
+        <v>124370264</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3142,28 +3151,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561429</v>
+        <v>561577</v>
       </c>
       <c r="R24" t="n">
-        <v>6397658</v>
+        <v>6397687</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3187,12 +3196,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3208,22 +3217,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370264</v>
+        <v>124358796</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3232,49 +3241,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561577</v>
+        <v>561533</v>
       </c>
       <c r="R25" t="n">
-        <v>6397687</v>
+        <v>6397592</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,12 +3308,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,29 +3322,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124359731</v>
+        <v>124370146</v>
       </c>
       <c r="B26" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3343,50 +3352,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561466</v>
+        <v>561565</v>
       </c>
       <c r="R26" t="n">
-        <v>6397610</v>
+        <v>6397707</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3424,28 +3432,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124369689</v>
+        <v>124359633</v>
       </c>
       <c r="B27" t="n">
-        <v>56714</v>
+        <v>95705</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3454,53 +3463,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561476</v>
+        <v>561533</v>
       </c>
       <c r="R27" t="n">
-        <v>6397662</v>
+        <v>6397592</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3524,12 +3521,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3667,10 +3664,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124358796</v>
+        <v>124359731</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3679,35 +3676,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3716,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561533</v>
+        <v>561466</v>
       </c>
       <c r="R29" t="n">
-        <v>6397592</v>
+        <v>6397610</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3771,14 +3768,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370019</v>
+        <v>124369964</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3826,10 +3823,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561503</v>
+        <v>561506</v>
       </c>
       <c r="R30" t="n">
-        <v>6397727</v>
+        <v>6397736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3889,7 +3886,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370146</v>
+        <v>124370108</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3937,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561565</v>
+        <v>561549</v>
       </c>
       <c r="R31" t="n">
-        <v>6397707</v>
+        <v>6397690</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4000,7 +3997,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370329</v>
+        <v>124370348</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4048,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561575</v>
+        <v>561531</v>
       </c>
       <c r="R32" t="n">
-        <v>6397630</v>
+        <v>6397636</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4111,10 +4108,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124369964</v>
+        <v>124358564</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4123,49 +4120,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561506</v>
+        <v>561553</v>
       </c>
       <c r="R33" t="n">
-        <v>6397736</v>
+        <v>6397632</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4203,29 +4192,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124358517</v>
+        <v>124369689</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4234,41 +4222,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561553</v>
+        <v>561476</v>
       </c>
       <c r="R34" t="n">
-        <v>6397632</v>
+        <v>6397662</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4312,19 +4312,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124370066</v>
+        <v>124358517</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4358,27 +4358,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561539</v>
+        <v>561553</v>
       </c>
       <c r="R35" t="n">
-        <v>6397729</v>
+        <v>6397632</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,29 +4408,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124359633</v>
+        <v>124370019</v>
       </c>
       <c r="B36" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4447,41 +4438,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561533</v>
+        <v>561503</v>
       </c>
       <c r="R36" t="n">
-        <v>6397592</v>
+        <v>6397727</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4519,25 +4518,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370348</v>
+        <v>124370368</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561531</v>
+        <v>561525</v>
       </c>
       <c r="R37" t="n">
-        <v>6397636</v>
+        <v>6397602</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124313836</v>
+        <v>124311790</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561563</v>
+        <v>561516</v>
       </c>
       <c r="R2" t="n">
-        <v>6397866</v>
+        <v>6397663</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311565</v>
+        <v>124311397</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561474</v>
+        <v>561425</v>
       </c>
       <c r="R3" t="n">
-        <v>6397726</v>
+        <v>6397700</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311342</v>
+        <v>124313772</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561426</v>
+        <v>561604</v>
       </c>
       <c r="R4" t="n">
-        <v>6397672</v>
+        <v>6397797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311630</v>
+        <v>124311718</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561506</v>
+        <v>561494</v>
       </c>
       <c r="R5" t="n">
-        <v>6397695</v>
+        <v>6397696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311718</v>
+        <v>124311366</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561494</v>
+        <v>561431</v>
       </c>
       <c r="R6" t="n">
-        <v>6397696</v>
+        <v>6397666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313606</v>
+        <v>124313669</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561566</v>
+        <v>561558</v>
       </c>
       <c r="R7" t="n">
-        <v>6397691</v>
+        <v>6397704</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124313669</v>
+        <v>124311750</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561558</v>
+        <v>561517</v>
       </c>
       <c r="R8" t="n">
-        <v>6397704</v>
+        <v>6397650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124311750</v>
+        <v>124311285</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561517</v>
+        <v>561408</v>
       </c>
       <c r="R9" t="n">
-        <v>6397650</v>
+        <v>6397661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311790</v>
+        <v>124311311</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561516</v>
+        <v>561426</v>
       </c>
       <c r="R10" t="n">
-        <v>6397663</v>
+        <v>6397656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311311</v>
+        <v>124311565</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,35 +1689,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1725,13 +1729,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561426</v>
+        <v>561474</v>
       </c>
       <c r="R11" t="n">
-        <v>6397656</v>
+        <v>6397726</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,7 +1773,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311500</v>
+        <v>124313606</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1836,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561472</v>
+        <v>561566</v>
       </c>
       <c r="R12" t="n">
-        <v>6397728</v>
+        <v>6397691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124313772</v>
+        <v>124313836</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,38 +1914,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561604</v>
+        <v>561563</v>
       </c>
       <c r="R13" t="n">
-        <v>6397797</v>
+        <v>6397866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311285</v>
+        <v>124311500</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561408</v>
+        <v>561472</v>
       </c>
       <c r="R14" t="n">
-        <v>6397661</v>
+        <v>6397728</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311366</v>
+        <v>124313702</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561431</v>
+        <v>561582</v>
       </c>
       <c r="R15" t="n">
-        <v>6397666</v>
+        <v>6397716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311397</v>
+        <v>124311630</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561425</v>
+        <v>561506</v>
       </c>
       <c r="R16" t="n">
-        <v>6397700</v>
+        <v>6397695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124313702</v>
+        <v>124311342</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561582</v>
+        <v>561426</v>
       </c>
       <c r="R18" t="n">
-        <v>6397716</v>
+        <v>6397672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124356739</v>
+        <v>124359633</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,25 +2580,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561558</v>
+        <v>561533</v>
       </c>
       <c r="R19" t="n">
-        <v>6397751</v>
+        <v>6397592</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,17 +2663,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124370066</v>
+        <v>124358796</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,49 +2682,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561539</v>
+        <v>561533</v>
       </c>
       <c r="R20" t="n">
-        <v>6397729</v>
+        <v>6397592</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2762,29 +2763,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124369824</v>
+        <v>124370019</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,35 +2793,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561459</v>
+        <v>561503</v>
       </c>
       <c r="R21" t="n">
-        <v>6397783</v>
+        <v>6397727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,17 +2867,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2889,14 +2885,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124368692</v>
+        <v>124358517</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2929,25 +2925,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561429</v>
+        <v>561553</v>
       </c>
       <c r="R22" t="n">
-        <v>6397658</v>
+        <v>6397632</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2976,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3000,17 +2987,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124370329</v>
+        <v>124359731</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,49 +3006,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561575</v>
+        <v>561466</v>
       </c>
       <c r="R23" t="n">
-        <v>6397630</v>
+        <v>6397610</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3099,26 +3087,25 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370264</v>
+        <v>124368692</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3151,28 +3138,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561577</v>
+        <v>561429</v>
       </c>
       <c r="R24" t="n">
-        <v>6397687</v>
+        <v>6397658</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3196,12 +3183,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3217,22 +3204,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124358796</v>
+        <v>124370348</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,50 +3228,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561533</v>
+        <v>561531</v>
       </c>
       <c r="R25" t="n">
-        <v>6397592</v>
+        <v>6397636</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3322,25 +3308,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370146</v>
+        <v>124356739</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3374,27 +3361,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561565</v>
+        <v>561558</v>
       </c>
       <c r="R26" t="n">
-        <v>6397707</v>
+        <v>6397751</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3432,29 +3411,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124359633</v>
+        <v>124369964</v>
       </c>
       <c r="B27" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3463,41 +3441,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561533</v>
+        <v>561506</v>
       </c>
       <c r="R27" t="n">
-        <v>6397592</v>
+        <v>6397736</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,25 +3521,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370087</v>
+        <v>124370264</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3601,10 +3588,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561547</v>
+        <v>561577</v>
       </c>
       <c r="R28" t="n">
-        <v>6397746</v>
+        <v>6397687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,12 +3618,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3664,10 +3651,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124359731</v>
+        <v>124370087</v>
       </c>
       <c r="B29" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3676,50 +3663,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561466</v>
+        <v>561547</v>
       </c>
       <c r="R29" t="n">
-        <v>6397610</v>
+        <v>6397746</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,28 +3743,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369964</v>
+        <v>124369824</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,35 +3774,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3823,10 +3810,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561506</v>
+        <v>561459</v>
       </c>
       <c r="R30" t="n">
-        <v>6397736</v>
+        <v>6397783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,13 +3848,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3879,14 +3870,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370108</v>
+        <v>124370066</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3934,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561549</v>
+        <v>561539</v>
       </c>
       <c r="R31" t="n">
-        <v>6397690</v>
+        <v>6397729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3997,7 +3988,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370348</v>
+        <v>124370329</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4045,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561531</v>
+        <v>561575</v>
       </c>
       <c r="R32" t="n">
-        <v>6397636</v>
+        <v>6397630</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4108,10 +4099,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124358564</v>
+        <v>124370146</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4120,41 +4111,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561553</v>
+        <v>561565</v>
       </c>
       <c r="R33" t="n">
-        <v>6397632</v>
+        <v>6397707</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,28 +4191,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124369689</v>
+        <v>124370368</v>
       </c>
       <c r="B34" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4222,39 +4222,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4262,13 +4258,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561476</v>
+        <v>561525</v>
       </c>
       <c r="R34" t="n">
-        <v>6397662</v>
+        <v>6397602</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4292,12 +4288,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4306,6 +4302,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4317,17 +4314,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124358517</v>
+        <v>124369689</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4336,41 +4333,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561553</v>
+        <v>561476</v>
       </c>
       <c r="R35" t="n">
-        <v>6397632</v>
+        <v>6397662</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4394,12 +4403,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4414,19 +4423,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370019</v>
+        <v>124370108</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4474,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561503</v>
+        <v>561549</v>
       </c>
       <c r="R36" t="n">
-        <v>6397727</v>
+        <v>6397690</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4537,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370368</v>
+        <v>124358564</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4549,49 +4558,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561525</v>
+        <v>561553</v>
       </c>
       <c r="R37" t="n">
-        <v>6397602</v>
+        <v>6397632</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4629,19 +4630,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124359633</v>
+        <v>124358796</v>
       </c>
       <c r="B19" t="n">
-        <v>95705</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,28 +2580,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
@@ -2670,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124358796</v>
+        <v>124359633</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,37 +2691,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124311790</v>
+        <v>124311342</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561516</v>
+        <v>561426</v>
       </c>
       <c r="R2" t="n">
-        <v>6397663</v>
+        <v>6397672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311397</v>
+        <v>124311311</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561425</v>
+        <v>561426</v>
       </c>
       <c r="R3" t="n">
-        <v>6397700</v>
+        <v>6397656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124313772</v>
+        <v>124311718</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561604</v>
+        <v>561494</v>
       </c>
       <c r="R4" t="n">
-        <v>6397797</v>
+        <v>6397696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311718</v>
+        <v>124313702</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561494</v>
+        <v>561582</v>
       </c>
       <c r="R5" t="n">
-        <v>6397696</v>
+        <v>6397716</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311366</v>
+        <v>124313606</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561431</v>
+        <v>561566</v>
       </c>
       <c r="R6" t="n">
-        <v>6397666</v>
+        <v>6397691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313669</v>
+        <v>124311397</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561558</v>
+        <v>561425</v>
       </c>
       <c r="R7" t="n">
-        <v>6397704</v>
+        <v>6397700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124311750</v>
+        <v>124313772</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,35 +1353,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561517</v>
+        <v>561604</v>
       </c>
       <c r="R8" t="n">
-        <v>6397650</v>
+        <v>6397797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124311285</v>
+        <v>124311565</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,35 +1467,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561408</v>
+        <v>561474</v>
       </c>
       <c r="R9" t="n">
-        <v>6397661</v>
+        <v>6397726</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1566,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311311</v>
+        <v>124311790</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1614,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561426</v>
+        <v>561516</v>
       </c>
       <c r="R10" t="n">
-        <v>6397656</v>
+        <v>6397663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311565</v>
+        <v>124311500</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,39 +1692,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1729,13 +1728,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561474</v>
+        <v>561472</v>
       </c>
       <c r="R11" t="n">
-        <v>6397726</v>
+        <v>6397728</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,6 +1772,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124313606</v>
+        <v>124313812</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561566</v>
+        <v>561599</v>
       </c>
       <c r="R12" t="n">
-        <v>6397691</v>
+        <v>6397835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124313836</v>
+        <v>124311285</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561563</v>
+        <v>561408</v>
       </c>
       <c r="R13" t="n">
-        <v>6397866</v>
+        <v>6397661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311500</v>
+        <v>124311366</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561472</v>
+        <v>561431</v>
       </c>
       <c r="R14" t="n">
-        <v>6397728</v>
+        <v>6397666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124313702</v>
+        <v>124311630</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561582</v>
+        <v>561506</v>
       </c>
       <c r="R15" t="n">
-        <v>6397716</v>
+        <v>6397695</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311630</v>
+        <v>124313836</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561506</v>
+        <v>561563</v>
       </c>
       <c r="R16" t="n">
-        <v>6397695</v>
+        <v>6397866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124313812</v>
+        <v>124313669</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561599</v>
+        <v>561558</v>
       </c>
       <c r="R17" t="n">
-        <v>6397835</v>
+        <v>6397704</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311342</v>
+        <v>124311750</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561426</v>
+        <v>561517</v>
       </c>
       <c r="R18" t="n">
-        <v>6397672</v>
+        <v>6397650</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124359633</v>
+        <v>124368692</v>
       </c>
       <c r="B20" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,38 +2691,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561533</v>
+        <v>561429</v>
       </c>
       <c r="R20" t="n">
-        <v>6397592</v>
+        <v>6397658</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2763,6 +2771,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2774,14 +2783,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370019</v>
+        <v>124370348</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2829,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561503</v>
+        <v>561531</v>
       </c>
       <c r="R21" t="n">
-        <v>6397727</v>
+        <v>6397636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124358517</v>
+        <v>124358564</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,25 +2913,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2987,17 +2996,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124359731</v>
+        <v>124358517</v>
       </c>
       <c r="B23" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,47 +3015,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561466</v>
+        <v>561553</v>
       </c>
       <c r="R23" t="n">
-        <v>6397610</v>
+        <v>6397632</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3098,14 +3098,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124368692</v>
+        <v>124370146</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3138,28 +3138,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561429</v>
+        <v>561565</v>
       </c>
       <c r="R24" t="n">
-        <v>6397658</v>
+        <v>6397707</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,22 +3204,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370348</v>
+        <v>124359731</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3228,49 +3228,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561531</v>
+        <v>561466</v>
       </c>
       <c r="R25" t="n">
-        <v>6397636</v>
+        <v>6397610</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3308,26 +3309,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124356739</v>
+        <v>124369964</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3361,19 +3361,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561558</v>
+        <v>561506</v>
       </c>
       <c r="R26" t="n">
-        <v>6397751</v>
+        <v>6397736</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3411,25 +3419,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124369964</v>
+        <v>124370329</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3477,10 +3486,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561506</v>
+        <v>561575</v>
       </c>
       <c r="R27" t="n">
-        <v>6397736</v>
+        <v>6397630</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,7 +3549,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370264</v>
+        <v>124370066</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3588,10 +3597,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561577</v>
+        <v>561539</v>
       </c>
       <c r="R28" t="n">
-        <v>6397687</v>
+        <v>6397729</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3618,12 +3627,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,7 +3660,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370087</v>
+        <v>124370019</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3699,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561547</v>
+        <v>561503</v>
       </c>
       <c r="R29" t="n">
-        <v>6397746</v>
+        <v>6397727</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3762,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369824</v>
+        <v>124359633</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3778,45 +3787,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561459</v>
+        <v>561533</v>
       </c>
       <c r="R30" t="n">
-        <v>6397783</v>
+        <v>6397592</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3846,11 +3847,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,22 +3861,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370066</v>
+        <v>124369824</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3889,35 +3885,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3925,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561539</v>
+        <v>561459</v>
       </c>
       <c r="R31" t="n">
-        <v>6397729</v>
+        <v>6397783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3963,13 +3959,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3981,17 +3981,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370329</v>
+        <v>124369689</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4000,35 +4000,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4036,13 +4040,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561575</v>
+        <v>561476</v>
       </c>
       <c r="R32" t="n">
-        <v>6397630</v>
+        <v>6397662</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4066,12 +4070,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,7 +4084,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4092,14 +4095,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370146</v>
+        <v>124370108</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4147,10 +4150,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561565</v>
+        <v>561549</v>
       </c>
       <c r="R33" t="n">
-        <v>6397707</v>
+        <v>6397690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4321,10 +4324,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124369689</v>
+        <v>124356739</v>
       </c>
       <c r="B35" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4333,53 +4336,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561476</v>
+        <v>561558</v>
       </c>
       <c r="R35" t="n">
-        <v>6397662</v>
+        <v>6397751</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4403,12 +4394,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4423,19 +4414,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370108</v>
+        <v>124370264</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4483,10 +4474,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561549</v>
+        <v>561577</v>
       </c>
       <c r="R36" t="n">
-        <v>6397690</v>
+        <v>6397687</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4513,12 +4504,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,10 +4537,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124358564</v>
+        <v>124370087</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4558,41 +4549,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561553</v>
+        <v>561547</v>
       </c>
       <c r="R37" t="n">
-        <v>6397632</v>
+        <v>6397746</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4630,18 +4629,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124311342</v>
+        <v>124311285</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561426</v>
+        <v>561408</v>
       </c>
       <c r="R2" t="n">
-        <v>6397672</v>
+        <v>6397661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311311</v>
+        <v>124313702</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561426</v>
+        <v>561582</v>
       </c>
       <c r="R3" t="n">
-        <v>6397656</v>
+        <v>6397716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311718</v>
+        <v>124313772</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561494</v>
+        <v>561604</v>
       </c>
       <c r="R4" t="n">
-        <v>6397696</v>
+        <v>6397797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124313702</v>
+        <v>124311342</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561582</v>
+        <v>561426</v>
       </c>
       <c r="R5" t="n">
-        <v>6397716</v>
+        <v>6397672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124313606</v>
+        <v>124311500</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561566</v>
+        <v>561472</v>
       </c>
       <c r="R6" t="n">
-        <v>6397691</v>
+        <v>6397728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124311397</v>
+        <v>124313606</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561425</v>
+        <v>561566</v>
       </c>
       <c r="R7" t="n">
-        <v>6397700</v>
+        <v>6397691</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124313772</v>
+        <v>124311311</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,38 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561604</v>
+        <v>561426</v>
       </c>
       <c r="R8" t="n">
-        <v>6397797</v>
+        <v>6397656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124311565</v>
+        <v>124313669</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,39 +1467,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561474</v>
+        <v>561558</v>
       </c>
       <c r="R9" t="n">
-        <v>6397726</v>
+        <v>6397704</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,6 +1547,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311790</v>
+        <v>124311397</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1617,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561516</v>
+        <v>561425</v>
       </c>
       <c r="R10" t="n">
-        <v>6397663</v>
+        <v>6397700</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311500</v>
+        <v>124311630</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1728,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561472</v>
+        <v>561506</v>
       </c>
       <c r="R11" t="n">
-        <v>6397728</v>
+        <v>6397695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1902,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124311285</v>
+        <v>124311718</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1950,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561408</v>
+        <v>561494</v>
       </c>
       <c r="R13" t="n">
-        <v>6397661</v>
+        <v>6397696</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311366</v>
+        <v>124311565</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2022,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561431</v>
+        <v>561474</v>
       </c>
       <c r="R14" t="n">
-        <v>6397666</v>
+        <v>6397726</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311630</v>
+        <v>124311750</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561506</v>
+        <v>561517</v>
       </c>
       <c r="R15" t="n">
-        <v>6397695</v>
+        <v>6397650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124313836</v>
+        <v>124311790</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561563</v>
+        <v>561516</v>
       </c>
       <c r="R16" t="n">
-        <v>6397866</v>
+        <v>6397663</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124313669</v>
+        <v>124311366</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561558</v>
+        <v>561431</v>
       </c>
       <c r="R17" t="n">
-        <v>6397704</v>
+        <v>6397666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311750</v>
+        <v>124313836</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561517</v>
+        <v>561563</v>
       </c>
       <c r="R18" t="n">
-        <v>6397650</v>
+        <v>6397866</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124358796</v>
+        <v>124369824</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,50 +2580,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561533</v>
+        <v>561459</v>
       </c>
       <c r="R19" t="n">
-        <v>6397592</v>
+        <v>6397783</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,6 +2652,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,19 +2671,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124368692</v>
+        <v>124370368</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2712,28 +2716,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561429</v>
+        <v>561525</v>
       </c>
       <c r="R20" t="n">
-        <v>6397658</v>
+        <v>6397602</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,19 +2782,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370348</v>
+        <v>124370108</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2838,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561531</v>
+        <v>561549</v>
       </c>
       <c r="R21" t="n">
-        <v>6397636</v>
+        <v>6397690</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124358564</v>
+        <v>124359633</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,25 +2917,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2941,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561553</v>
+        <v>561533</v>
       </c>
       <c r="R22" t="n">
-        <v>6397632</v>
+        <v>6397592</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,17 +3000,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124358517</v>
+        <v>124369689</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,41 +3019,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561553</v>
+        <v>561476</v>
       </c>
       <c r="R23" t="n">
-        <v>6397632</v>
+        <v>6397662</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3073,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,12 +3109,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3216,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124359731</v>
+        <v>124368692</v>
       </c>
       <c r="B25" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3228,47 +3244,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561466</v>
+        <v>561429</v>
       </c>
       <c r="R25" t="n">
-        <v>6397610</v>
+        <v>6397658</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3309,6 +3324,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3327,7 +3343,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369964</v>
+        <v>124370087</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3375,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561506</v>
+        <v>561547</v>
       </c>
       <c r="R26" t="n">
-        <v>6397736</v>
+        <v>6397746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,7 +3454,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370329</v>
+        <v>124370348</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3486,10 +3502,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561575</v>
+        <v>561531</v>
       </c>
       <c r="R27" t="n">
-        <v>6397630</v>
+        <v>6397636</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3565,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370066</v>
+        <v>124370329</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3597,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561539</v>
+        <v>561575</v>
       </c>
       <c r="R28" t="n">
-        <v>6397729</v>
+        <v>6397630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370019</v>
+        <v>124358564</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3672,49 +3688,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561503</v>
+        <v>561553</v>
       </c>
       <c r="R29" t="n">
-        <v>6397727</v>
+        <v>6397632</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,29 +3760,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124359633</v>
+        <v>124356739</v>
       </c>
       <c r="B30" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,25 +3790,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3818,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561533</v>
+        <v>561558</v>
       </c>
       <c r="R30" t="n">
-        <v>6397592</v>
+        <v>6397751</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3866,17 +3873,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124369824</v>
+        <v>124359731</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3889,45 +3896,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561459</v>
+        <v>561466</v>
       </c>
       <c r="R31" t="n">
-        <v>6397783</v>
+        <v>6397610</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3957,11 +3965,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,22 +3979,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124369689</v>
+        <v>124369964</v>
       </c>
       <c r="B32" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4000,39 +4003,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4040,13 +4039,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561476</v>
+        <v>561506</v>
       </c>
       <c r="R32" t="n">
-        <v>6397662</v>
+        <v>6397736</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4070,12 +4069,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,6 +4083,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4095,14 +4095,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370108</v>
+        <v>124370019</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561549</v>
+        <v>561503</v>
       </c>
       <c r="R33" t="n">
-        <v>6397690</v>
+        <v>6397727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124370368</v>
+        <v>124358796</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4225,49 +4225,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561525</v>
+        <v>561533</v>
       </c>
       <c r="R34" t="n">
-        <v>6397602</v>
+        <v>6397592</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,26 +4306,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124356739</v>
+        <v>124370066</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4358,19 +4358,27 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561558</v>
+        <v>561539</v>
       </c>
       <c r="R35" t="n">
-        <v>6397751</v>
+        <v>6397729</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4408,18 +4416,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4537,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370087</v>
+        <v>124358517</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4571,27 +4580,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561547</v>
+        <v>561553</v>
       </c>
       <c r="R37" t="n">
-        <v>6397746</v>
+        <v>6397632</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4629,19 +4630,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124311285</v>
+        <v>124313836</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561408</v>
+        <v>561563</v>
       </c>
       <c r="R2" t="n">
-        <v>6397661</v>
+        <v>6397866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124313772</v>
+        <v>124311500</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561604</v>
+        <v>561472</v>
       </c>
       <c r="R4" t="n">
-        <v>6397797</v>
+        <v>6397728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311342</v>
+        <v>124313772</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561426</v>
+        <v>561604</v>
       </c>
       <c r="R5" t="n">
-        <v>6397672</v>
+        <v>6397797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311500</v>
+        <v>124311565</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561472</v>
+        <v>561474</v>
       </c>
       <c r="R6" t="n">
-        <v>6397728</v>
+        <v>6397726</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313606</v>
+        <v>124311790</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1281,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561566</v>
+        <v>561516</v>
       </c>
       <c r="R7" t="n">
-        <v>6397691</v>
+        <v>6397663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1455,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124313669</v>
+        <v>124311285</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561558</v>
+        <v>561408</v>
       </c>
       <c r="R9" t="n">
-        <v>6397704</v>
+        <v>6397661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311397</v>
+        <v>124311718</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1614,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561425</v>
+        <v>561494</v>
       </c>
       <c r="R10" t="n">
-        <v>6397700</v>
+        <v>6397696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311630</v>
+        <v>124311750</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1725,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561506</v>
+        <v>561517</v>
       </c>
       <c r="R11" t="n">
-        <v>6397695</v>
+        <v>6397650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124313812</v>
+        <v>124313606</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1836,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561599</v>
+        <v>561566</v>
       </c>
       <c r="R12" t="n">
-        <v>6397835</v>
+        <v>6397691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124311718</v>
+        <v>124313669</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1947,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561494</v>
+        <v>561558</v>
       </c>
       <c r="R13" t="n">
-        <v>6397696</v>
+        <v>6397704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311565</v>
+        <v>124311397</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,39 +2025,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,13 +2061,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561474</v>
+        <v>561425</v>
       </c>
       <c r="R14" t="n">
-        <v>6397726</v>
+        <v>6397700</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,6 +2105,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311750</v>
+        <v>124311342</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561517</v>
+        <v>561426</v>
       </c>
       <c r="R15" t="n">
-        <v>6397650</v>
+        <v>6397672</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311790</v>
+        <v>124311366</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561516</v>
+        <v>561431</v>
       </c>
       <c r="R16" t="n">
-        <v>6397663</v>
+        <v>6397666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124311366</v>
+        <v>124313812</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561431</v>
+        <v>561599</v>
       </c>
       <c r="R17" t="n">
-        <v>6397666</v>
+        <v>6397835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124313836</v>
+        <v>124311630</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561563</v>
+        <v>561506</v>
       </c>
       <c r="R18" t="n">
-        <v>6397866</v>
+        <v>6397695</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124369824</v>
+        <v>124370019</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,35 +2580,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561459</v>
+        <v>561503</v>
       </c>
       <c r="R19" t="n">
-        <v>6397783</v>
+        <v>6397727</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,17 +2654,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2676,17 +2672,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124370368</v>
+        <v>124369824</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2695,35 +2691,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2731,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561525</v>
+        <v>561459</v>
       </c>
       <c r="R20" t="n">
-        <v>6397602</v>
+        <v>6397783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,13 +2765,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2787,17 +2787,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370108</v>
+        <v>124358796</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,49 +2806,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561549</v>
+        <v>561533</v>
       </c>
       <c r="R21" t="n">
-        <v>6397690</v>
+        <v>6397592</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2886,29 +2887,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124359633</v>
+        <v>124370146</v>
       </c>
       <c r="B22" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,41 +2917,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561533</v>
+        <v>561565</v>
       </c>
       <c r="R22" t="n">
-        <v>6397592</v>
+        <v>6397707</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2989,18 +2997,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3121,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370146</v>
+        <v>124370108</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3169,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561565</v>
+        <v>561549</v>
       </c>
       <c r="R24" t="n">
-        <v>6397707</v>
+        <v>6397690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3232,7 +3241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124368692</v>
+        <v>124370066</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3265,28 +3274,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561429</v>
+        <v>561539</v>
       </c>
       <c r="R25" t="n">
-        <v>6397658</v>
+        <v>6397729</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3331,19 +3340,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370087</v>
+        <v>124369964</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3391,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561547</v>
+        <v>561506</v>
       </c>
       <c r="R26" t="n">
-        <v>6397746</v>
+        <v>6397736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,7 +3463,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370348</v>
+        <v>124368692</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3487,28 +3496,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561531</v>
+        <v>561429</v>
       </c>
       <c r="R27" t="n">
-        <v>6397636</v>
+        <v>6397658</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3553,19 +3562,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370329</v>
+        <v>124358517</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3599,27 +3608,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561575</v>
+        <v>561553</v>
       </c>
       <c r="R28" t="n">
-        <v>6397630</v>
+        <v>6397632</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3657,29 +3658,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124358564</v>
+        <v>124370368</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,41 +3688,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561553</v>
+        <v>561525</v>
       </c>
       <c r="R29" t="n">
-        <v>6397632</v>
+        <v>6397602</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3760,28 +3768,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124356739</v>
+        <v>124359731</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3790,38 +3799,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561558</v>
+        <v>561466</v>
       </c>
       <c r="R30" t="n">
-        <v>6397751</v>
+        <v>6397610</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3873,17 +3891,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124359731</v>
+        <v>124370087</v>
       </c>
       <c r="B31" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3892,50 +3910,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561466</v>
+        <v>561547</v>
       </c>
       <c r="R31" t="n">
-        <v>6397610</v>
+        <v>6397746</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3973,28 +3990,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124369964</v>
+        <v>124359633</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4003,49 +4021,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561506</v>
+        <v>561533</v>
       </c>
       <c r="R32" t="n">
-        <v>6397736</v>
+        <v>6397592</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,26 +4093,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370019</v>
+        <v>124356739</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4136,27 +4145,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561503</v>
+        <v>561558</v>
       </c>
       <c r="R33" t="n">
-        <v>6397727</v>
+        <v>6397751</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,29 +4195,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124358796</v>
+        <v>124370329</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4225,50 +4225,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561533</v>
+        <v>561575</v>
       </c>
       <c r="R34" t="n">
-        <v>6397592</v>
+        <v>6397630</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4306,25 +4305,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124370066</v>
+        <v>124370348</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561539</v>
+        <v>561531</v>
       </c>
       <c r="R35" t="n">
-        <v>6397729</v>
+        <v>6397636</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124358517</v>
+        <v>124358564</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4558,25 +4558,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311342</v>
+        <v>124311366</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561426</v>
+        <v>561431</v>
       </c>
       <c r="R15" t="n">
-        <v>6397672</v>
+        <v>6397666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311366</v>
+        <v>124311342</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561431</v>
+        <v>561426</v>
       </c>
       <c r="R16" t="n">
-        <v>6397666</v>
+        <v>6397672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124359731</v>
+        <v>124370087</v>
       </c>
       <c r="B30" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3799,50 +3799,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561466</v>
+        <v>561547</v>
       </c>
       <c r="R30" t="n">
-        <v>6397610</v>
+        <v>6397746</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3880,28 +3879,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370087</v>
+        <v>124359731</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,49 +3910,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561547</v>
+        <v>561466</v>
       </c>
       <c r="R31" t="n">
-        <v>6397746</v>
+        <v>6397610</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3990,19 +3991,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124313836</v>
+        <v>124313772</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561563</v>
+        <v>561604</v>
       </c>
       <c r="R2" t="n">
-        <v>6397866</v>
+        <v>6397797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124313702</v>
+        <v>124313812</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561582</v>
+        <v>561599</v>
       </c>
       <c r="R3" t="n">
-        <v>6397716</v>
+        <v>6397835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311500</v>
+        <v>124311750</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561472</v>
+        <v>561517</v>
       </c>
       <c r="R4" t="n">
-        <v>6397728</v>
+        <v>6397650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124313772</v>
+        <v>124311366</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561604</v>
+        <v>561431</v>
       </c>
       <c r="R5" t="n">
-        <v>6397797</v>
+        <v>6397666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311565</v>
+        <v>124311397</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561474</v>
+        <v>561425</v>
       </c>
       <c r="R6" t="n">
-        <v>6397726</v>
+        <v>6397700</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124311790</v>
+        <v>124313702</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1284,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561516</v>
+        <v>561582</v>
       </c>
       <c r="R7" t="n">
-        <v>6397663</v>
+        <v>6397716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124311311</v>
+        <v>124311565</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,35 +1356,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561426</v>
+        <v>561474</v>
       </c>
       <c r="R8" t="n">
-        <v>6397656</v>
+        <v>6397726</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311718</v>
+        <v>124313669</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561494</v>
+        <v>561558</v>
       </c>
       <c r="R10" t="n">
-        <v>6397696</v>
+        <v>6397704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311750</v>
+        <v>124311311</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561517</v>
+        <v>561426</v>
       </c>
       <c r="R11" t="n">
-        <v>6397650</v>
+        <v>6397656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124313606</v>
+        <v>124311500</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561566</v>
+        <v>561472</v>
       </c>
       <c r="R12" t="n">
-        <v>6397691</v>
+        <v>6397728</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124313669</v>
+        <v>124311630</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561558</v>
+        <v>561506</v>
       </c>
       <c r="R13" t="n">
-        <v>6397704</v>
+        <v>6397695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311397</v>
+        <v>124313836</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561425</v>
+        <v>561563</v>
       </c>
       <c r="R14" t="n">
-        <v>6397700</v>
+        <v>6397866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311366</v>
+        <v>124311718</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561431</v>
+        <v>561494</v>
       </c>
       <c r="R15" t="n">
-        <v>6397666</v>
+        <v>6397696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124313812</v>
+        <v>124311790</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561599</v>
+        <v>561516</v>
       </c>
       <c r="R17" t="n">
-        <v>6397835</v>
+        <v>6397663</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311630</v>
+        <v>124313606</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561506</v>
+        <v>561566</v>
       </c>
       <c r="R18" t="n">
-        <v>6397695</v>
+        <v>6397691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370019</v>
+        <v>124368692</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2601,28 +2601,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561503</v>
+        <v>561429</v>
       </c>
       <c r="R19" t="n">
-        <v>6397727</v>
+        <v>6397658</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,22 +2667,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124369824</v>
+        <v>124370019</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,35 +2691,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561459</v>
+        <v>561503</v>
       </c>
       <c r="R20" t="n">
-        <v>6397783</v>
+        <v>6397727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,17 +2765,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2787,17 +2783,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124358796</v>
+        <v>124370108</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,50 +2802,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561533</v>
+        <v>561549</v>
       </c>
       <c r="R21" t="n">
-        <v>6397592</v>
+        <v>6397690</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,28 +2882,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124370146</v>
+        <v>124369824</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,35 +2913,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561565</v>
+        <v>561459</v>
       </c>
       <c r="R22" t="n">
-        <v>6397707</v>
+        <v>6397783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2991,13 +2987,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3130,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370108</v>
+        <v>124370066</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561549</v>
+        <v>561539</v>
       </c>
       <c r="R24" t="n">
-        <v>6397690</v>
+        <v>6397729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370066</v>
+        <v>124369964</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561539</v>
+        <v>561506</v>
       </c>
       <c r="R25" t="n">
-        <v>6397729</v>
+        <v>6397736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369964</v>
+        <v>124370087</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561506</v>
+        <v>561547</v>
       </c>
       <c r="R26" t="n">
-        <v>6397736</v>
+        <v>6397746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124368692</v>
+        <v>124359731</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3475,46 +3475,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561429</v>
+        <v>561466</v>
       </c>
       <c r="R27" t="n">
-        <v>6397658</v>
+        <v>6397610</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3555,7 +3556,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370368</v>
+        <v>124358564</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,49 +3688,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561525</v>
+        <v>561553</v>
       </c>
       <c r="R29" t="n">
-        <v>6397602</v>
+        <v>6397632</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3768,29 +3760,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370087</v>
+        <v>124359633</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3799,49 +3790,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561547</v>
+        <v>561533</v>
       </c>
       <c r="R30" t="n">
-        <v>6397746</v>
+        <v>6397592</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,29 +3862,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124359731</v>
+        <v>124356739</v>
       </c>
       <c r="B31" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,47 +3892,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561466</v>
+        <v>561558</v>
       </c>
       <c r="R31" t="n">
-        <v>6397610</v>
+        <v>6397751</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4002,17 +3975,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124359633</v>
+        <v>124370348</v>
       </c>
       <c r="B32" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4021,41 +3994,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561533</v>
+        <v>561531</v>
       </c>
       <c r="R32" t="n">
-        <v>6397592</v>
+        <v>6397636</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4093,25 +4074,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124356739</v>
+        <v>124370368</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4145,19 +4127,27 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561558</v>
+        <v>561525</v>
       </c>
       <c r="R33" t="n">
-        <v>6397751</v>
+        <v>6397602</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4195,18 +4185,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4317,14 +4308,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124370348</v>
+        <v>124370264</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4372,10 +4363,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561531</v>
+        <v>561577</v>
       </c>
       <c r="R35" t="n">
-        <v>6397636</v>
+        <v>6397687</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,12 +4393,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4428,17 +4419,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370264</v>
+        <v>124358796</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4447,49 +4438,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561577</v>
+        <v>561533</v>
       </c>
       <c r="R36" t="n">
-        <v>6397687</v>
+        <v>6397592</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4513,12 +4505,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4527,29 +4519,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124358564</v>
+        <v>124370146</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4558,41 +4549,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561553</v>
+        <v>561565</v>
       </c>
       <c r="R37" t="n">
-        <v>6397632</v>
+        <v>6397707</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4630,18 +4629,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370108</v>
+        <v>124369824</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,35 +2802,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561549</v>
+        <v>561459</v>
       </c>
       <c r="R21" t="n">
-        <v>6397690</v>
+        <v>6397783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,13 +2876,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2894,17 +2898,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124369824</v>
+        <v>124370108</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,35 +2917,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2949,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561459</v>
+        <v>561549</v>
       </c>
       <c r="R22" t="n">
-        <v>6397783</v>
+        <v>6397690</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2987,17 +2991,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124359731</v>
+        <v>124358517</v>
       </c>
       <c r="B27" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3475,47 +3475,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561466</v>
+        <v>561553</v>
       </c>
       <c r="R27" t="n">
-        <v>6397610</v>
+        <v>6397632</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,17 +3558,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124358517</v>
+        <v>124359731</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3586,38 +3577,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561553</v>
+        <v>561466</v>
       </c>
       <c r="R28" t="n">
-        <v>6397632</v>
+        <v>6397610</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124358564</v>
+        <v>124359633</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,25 +3688,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561553</v>
+        <v>561533</v>
       </c>
       <c r="R29" t="n">
-        <v>6397632</v>
+        <v>6397592</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3771,17 +3771,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124359633</v>
+        <v>124358564</v>
       </c>
       <c r="B30" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3790,25 +3790,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561533</v>
+        <v>561553</v>
       </c>
       <c r="R30" t="n">
-        <v>6397592</v>
+        <v>6397632</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124370264</v>
+        <v>124358796</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4327,49 +4327,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561577</v>
+        <v>561533</v>
       </c>
       <c r="R35" t="n">
-        <v>6397687</v>
+        <v>6397592</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4393,12 +4394,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4407,29 +4408,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124358796</v>
+        <v>124370264</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4438,50 +4438,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561533</v>
+        <v>561577</v>
       </c>
       <c r="R36" t="n">
-        <v>6397592</v>
+        <v>6397687</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4505,12 +4504,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4519,18 +4518,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124313772</v>
+        <v>124313669</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561604</v>
+        <v>561558</v>
       </c>
       <c r="R2" t="n">
-        <v>6397797</v>
+        <v>6397704</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124313812</v>
+        <v>124311718</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561599</v>
+        <v>561494</v>
       </c>
       <c r="R3" t="n">
-        <v>6397835</v>
+        <v>6397696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311750</v>
+        <v>124311342</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561517</v>
+        <v>561426</v>
       </c>
       <c r="R4" t="n">
-        <v>6397650</v>
+        <v>6397672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311366</v>
+        <v>124311311</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561431</v>
+        <v>561426</v>
       </c>
       <c r="R5" t="n">
-        <v>6397666</v>
+        <v>6397656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1233,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313702</v>
+        <v>124311750</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561582</v>
+        <v>561517</v>
       </c>
       <c r="R7" t="n">
-        <v>6397716</v>
+        <v>6397650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1458,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124311285</v>
+        <v>124313702</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1506,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561408</v>
+        <v>561582</v>
       </c>
       <c r="R9" t="n">
-        <v>6397661</v>
+        <v>6397716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124313669</v>
+        <v>124311366</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1617,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561558</v>
+        <v>561431</v>
       </c>
       <c r="R10" t="n">
-        <v>6397704</v>
+        <v>6397666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311311</v>
+        <v>124313812</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1728,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561426</v>
+        <v>561599</v>
       </c>
       <c r="R11" t="n">
-        <v>6397656</v>
+        <v>6397835</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311500</v>
+        <v>124311630</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1839,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561472</v>
+        <v>561506</v>
       </c>
       <c r="R12" t="n">
-        <v>6397728</v>
+        <v>6397695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124311630</v>
+        <v>124311500</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1950,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561506</v>
+        <v>561472</v>
       </c>
       <c r="R13" t="n">
-        <v>6397695</v>
+        <v>6397728</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124313836</v>
+        <v>124311790</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2061,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561563</v>
+        <v>561516</v>
       </c>
       <c r="R14" t="n">
-        <v>6397866</v>
+        <v>6397663</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311718</v>
+        <v>124311285</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561494</v>
+        <v>561408</v>
       </c>
       <c r="R15" t="n">
-        <v>6397696</v>
+        <v>6397661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311342</v>
+        <v>124313836</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561426</v>
+        <v>561563</v>
       </c>
       <c r="R16" t="n">
-        <v>6397672</v>
+        <v>6397866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124311790</v>
+        <v>124313772</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,35 +2355,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561516</v>
+        <v>561604</v>
       </c>
       <c r="R17" t="n">
-        <v>6397663</v>
+        <v>6397797</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124368692</v>
+        <v>124370329</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2601,28 +2601,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561429</v>
+        <v>561575</v>
       </c>
       <c r="R19" t="n">
-        <v>6397658</v>
+        <v>6397630</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,19 +2667,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124370019</v>
+        <v>124368692</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2712,28 +2712,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561503</v>
+        <v>561429</v>
       </c>
       <c r="R20" t="n">
-        <v>6397727</v>
+        <v>6397658</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124369824</v>
+        <v>124370146</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,35 +2802,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561459</v>
+        <v>561565</v>
       </c>
       <c r="R21" t="n">
-        <v>6397783</v>
+        <v>6397707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,17 +2876,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,14 +2894,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124370108</v>
+        <v>124358517</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2939,27 +2935,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561549</v>
+        <v>561553</v>
       </c>
       <c r="R22" t="n">
-        <v>6397690</v>
+        <v>6397632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,29 +2985,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369689</v>
+        <v>124359731</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>95705</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,53 +3015,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561476</v>
+        <v>561466</v>
       </c>
       <c r="R23" t="n">
-        <v>6397662</v>
+        <v>6397610</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,12 +3082,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3118,19 +3102,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370066</v>
+        <v>124370108</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3178,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561539</v>
+        <v>561549</v>
       </c>
       <c r="R24" t="n">
-        <v>6397729</v>
+        <v>6397690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3241,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369964</v>
+        <v>124358796</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,49 +3237,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561506</v>
+        <v>561533</v>
       </c>
       <c r="R25" t="n">
-        <v>6397736</v>
+        <v>6397592</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,26 +3318,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370087</v>
+        <v>124370066</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3400,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561547</v>
+        <v>561539</v>
       </c>
       <c r="R26" t="n">
-        <v>6397746</v>
+        <v>6397729</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3447,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124358517</v>
+        <v>124370019</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3497,19 +3481,27 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561553</v>
+        <v>561503</v>
       </c>
       <c r="R27" t="n">
-        <v>6397632</v>
+        <v>6397727</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3547,28 +3539,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124359731</v>
+        <v>124358564</v>
       </c>
       <c r="B28" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,47 +3570,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561466</v>
+        <v>561553</v>
       </c>
       <c r="R28" t="n">
-        <v>6397610</v>
+        <v>6397632</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3669,17 +3653,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124359633</v>
+        <v>124370264</v>
       </c>
       <c r="B29" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3688,41 +3672,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561533</v>
+        <v>561577</v>
       </c>
       <c r="R29" t="n">
-        <v>6397592</v>
+        <v>6397687</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3746,12 +3738,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,28 +3752,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124358564</v>
+        <v>124359633</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3790,25 +3783,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3818,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561553</v>
+        <v>561533</v>
       </c>
       <c r="R30" t="n">
-        <v>6397632</v>
+        <v>6397592</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3873,14 +3866,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124356739</v>
+        <v>124370348</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3914,19 +3907,27 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561558</v>
+        <v>561531</v>
       </c>
       <c r="R31" t="n">
-        <v>6397751</v>
+        <v>6397636</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3964,28 +3965,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370348</v>
+        <v>124369824</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3994,35 +3996,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4030,10 +4032,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561531</v>
+        <v>561459</v>
       </c>
       <c r="R32" t="n">
-        <v>6397636</v>
+        <v>6397783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,13 +4070,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4086,7 +4092,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4204,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124370329</v>
+        <v>124369689</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4216,35 +4222,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4252,13 +4262,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561575</v>
+        <v>561476</v>
       </c>
       <c r="R34" t="n">
-        <v>6397630</v>
+        <v>6397662</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4282,12 +4292,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4296,7 +4306,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4308,17 +4317,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124358796</v>
+        <v>124370087</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4327,50 +4336,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561533</v>
+        <v>561547</v>
       </c>
       <c r="R35" t="n">
-        <v>6397592</v>
+        <v>6397746</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4408,25 +4416,26 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370264</v>
+        <v>124369964</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4474,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561577</v>
+        <v>561506</v>
       </c>
       <c r="R36" t="n">
-        <v>6397687</v>
+        <v>6397736</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,12 +4513,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4530,14 +4539,14 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370146</v>
+        <v>124356739</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4571,27 +4580,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561565</v>
+        <v>561558</v>
       </c>
       <c r="R37" t="n">
-        <v>6397707</v>
+        <v>6397751</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4629,19 +4630,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124313669</v>
+        <v>124313702</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561558</v>
+        <v>561582</v>
       </c>
       <c r="R2" t="n">
-        <v>6397704</v>
+        <v>6397716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311718</v>
+        <v>124311366</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561494</v>
+        <v>561431</v>
       </c>
       <c r="R3" t="n">
-        <v>6397696</v>
+        <v>6397666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311342</v>
+        <v>124311311</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -948,7 +948,7 @@
         <v>561426</v>
       </c>
       <c r="R4" t="n">
-        <v>6397672</v>
+        <v>6397656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311311</v>
+        <v>124311718</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561426</v>
+        <v>561494</v>
       </c>
       <c r="R5" t="n">
-        <v>6397656</v>
+        <v>6397696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311397</v>
+        <v>124311790</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561425</v>
+        <v>561516</v>
       </c>
       <c r="R6" t="n">
-        <v>6397700</v>
+        <v>6397663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124311750</v>
+        <v>124313836</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561517</v>
+        <v>561563</v>
       </c>
       <c r="R7" t="n">
-        <v>6397650</v>
+        <v>6397866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124313702</v>
+        <v>124311397</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561582</v>
+        <v>561425</v>
       </c>
       <c r="R9" t="n">
-        <v>6397716</v>
+        <v>6397700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311366</v>
+        <v>124311630</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561431</v>
+        <v>561506</v>
       </c>
       <c r="R10" t="n">
-        <v>6397666</v>
+        <v>6397695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124313812</v>
+        <v>124311750</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561599</v>
+        <v>561517</v>
       </c>
       <c r="R11" t="n">
-        <v>6397835</v>
+        <v>6397650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311630</v>
+        <v>124311342</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561506</v>
+        <v>561426</v>
       </c>
       <c r="R12" t="n">
-        <v>6397695</v>
+        <v>6397672</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124311500</v>
+        <v>124313772</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,35 +1911,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1947,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561472</v>
+        <v>561604</v>
       </c>
       <c r="R13" t="n">
-        <v>6397728</v>
+        <v>6397797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124311790</v>
+        <v>124313669</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2058,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561516</v>
+        <v>561558</v>
       </c>
       <c r="R14" t="n">
-        <v>6397663</v>
+        <v>6397704</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124311285</v>
+        <v>124313606</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2169,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561408</v>
+        <v>561566</v>
       </c>
       <c r="R15" t="n">
-        <v>6397661</v>
+        <v>6397691</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124313836</v>
+        <v>124311500</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2280,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561563</v>
+        <v>561472</v>
       </c>
       <c r="R16" t="n">
-        <v>6397866</v>
+        <v>6397728</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124313772</v>
+        <v>124313812</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,38 +2358,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561604</v>
+        <v>561599</v>
       </c>
       <c r="R17" t="n">
-        <v>6397797</v>
+        <v>6397835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124313606</v>
+        <v>124311285</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561566</v>
+        <v>561408</v>
       </c>
       <c r="R18" t="n">
-        <v>6397691</v>
+        <v>6397661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370329</v>
+        <v>124358517</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2602,27 +2602,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561575</v>
+        <v>561553</v>
       </c>
       <c r="R19" t="n">
-        <v>6397630</v>
+        <v>6397632</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,26 +2652,25 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124368692</v>
+        <v>124370146</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2712,28 +2703,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561429</v>
+        <v>561565</v>
       </c>
       <c r="R20" t="n">
-        <v>6397658</v>
+        <v>6397707</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,19 +2769,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370146</v>
+        <v>124370348</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2838,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561565</v>
+        <v>561531</v>
       </c>
       <c r="R21" t="n">
-        <v>6397707</v>
+        <v>6397636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124358517</v>
+        <v>124370329</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2935,19 +2926,27 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561553</v>
+        <v>561575</v>
       </c>
       <c r="R22" t="n">
-        <v>6397632</v>
+        <v>6397630</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,28 +2984,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124359731</v>
+        <v>124369824</v>
       </c>
       <c r="B23" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,46 +3019,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561466</v>
+        <v>561459</v>
       </c>
       <c r="R23" t="n">
-        <v>6397610</v>
+        <v>6397783</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,6 +3087,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,19 +3106,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370108</v>
+        <v>124370066</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3162,10 +3166,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561549</v>
+        <v>561539</v>
       </c>
       <c r="R24" t="n">
-        <v>6397690</v>
+        <v>6397729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3225,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124358796</v>
+        <v>124370019</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,50 +3241,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561533</v>
+        <v>561503</v>
       </c>
       <c r="R25" t="n">
-        <v>6397592</v>
+        <v>6397727</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3318,25 +3321,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370066</v>
+        <v>124356739</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3370,27 +3374,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561539</v>
+        <v>561558</v>
       </c>
       <c r="R26" t="n">
-        <v>6397729</v>
+        <v>6397751</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3428,29 +3424,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370019</v>
+        <v>124358796</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3459,49 +3454,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561503</v>
+        <v>561533</v>
       </c>
       <c r="R27" t="n">
-        <v>6397727</v>
+        <v>6397592</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3539,29 +3535,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124358564</v>
+        <v>124370368</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3570,41 +3565,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561553</v>
+        <v>561525</v>
       </c>
       <c r="R28" t="n">
-        <v>6397632</v>
+        <v>6397602</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3642,28 +3645,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370264</v>
+        <v>124359731</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3672,49 +3676,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561577</v>
+        <v>561466</v>
       </c>
       <c r="R29" t="n">
-        <v>6397687</v>
+        <v>6397610</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3738,12 +3743,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3752,29 +3757,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124359633</v>
+        <v>124370087</v>
       </c>
       <c r="B30" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,41 +3787,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561533</v>
+        <v>561547</v>
       </c>
       <c r="R30" t="n">
-        <v>6397592</v>
+        <v>6397746</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3855,28 +3867,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370348</v>
+        <v>124359633</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3885,49 +3898,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561531</v>
+        <v>561533</v>
       </c>
       <c r="R31" t="n">
-        <v>6397636</v>
+        <v>6397592</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3965,29 +3970,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124369824</v>
+        <v>124369964</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,35 +4000,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4032,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561459</v>
+        <v>561506</v>
       </c>
       <c r="R32" t="n">
-        <v>6397783</v>
+        <v>6397736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,17 +4074,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4092,14 +4092,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370368</v>
+        <v>124370108</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561525</v>
+        <v>561549</v>
       </c>
       <c r="R33" t="n">
-        <v>6397602</v>
+        <v>6397690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124369689</v>
+        <v>124358564</v>
       </c>
       <c r="B34" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4226,16 +4226,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4243,32 +4243,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561476</v>
+        <v>561553</v>
       </c>
       <c r="R34" t="n">
-        <v>6397662</v>
+        <v>6397632</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4292,12 +4280,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4312,22 +4300,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124370087</v>
+        <v>124369689</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4336,35 +4324,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4372,13 +4364,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561547</v>
+        <v>561476</v>
       </c>
       <c r="R35" t="n">
-        <v>6397746</v>
+        <v>6397662</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4402,12 +4394,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4416,7 +4408,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4428,14 +4419,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124369964</v>
+        <v>124368692</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4468,28 +4459,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561506</v>
+        <v>561429</v>
       </c>
       <c r="R36" t="n">
-        <v>6397736</v>
+        <v>6397658</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4534,19 +4525,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124356739</v>
+        <v>124370264</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4580,19 +4571,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561558</v>
+        <v>561577</v>
       </c>
       <c r="R37" t="n">
-        <v>6397751</v>
+        <v>6397687</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4616,12 +4615,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4630,18 +4629,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124313702</v>
+        <v>124313606</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561582</v>
+        <v>561566</v>
       </c>
       <c r="R2" t="n">
-        <v>6397716</v>
+        <v>6397691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124311366</v>
+        <v>124313669</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561431</v>
+        <v>561558</v>
       </c>
       <c r="R3" t="n">
-        <v>6397666</v>
+        <v>6397704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124311311</v>
+        <v>124313772</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561426</v>
+        <v>561604</v>
       </c>
       <c r="R4" t="n">
-        <v>6397656</v>
+        <v>6397797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124311718</v>
+        <v>124311500</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561494</v>
+        <v>561472</v>
       </c>
       <c r="R5" t="n">
-        <v>6397696</v>
+        <v>6397728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124311790</v>
+        <v>124311750</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561516</v>
+        <v>561517</v>
       </c>
       <c r="R6" t="n">
-        <v>6397663</v>
+        <v>6397650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313836</v>
+        <v>124313812</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561563</v>
+        <v>561599</v>
       </c>
       <c r="R7" t="n">
-        <v>6397866</v>
+        <v>6397835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124311565</v>
+        <v>124313702</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561474</v>
+        <v>561582</v>
       </c>
       <c r="R8" t="n">
-        <v>6397726</v>
+        <v>6397716</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,6 +1436,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124311397</v>
+        <v>124311285</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561425</v>
+        <v>561408</v>
       </c>
       <c r="R9" t="n">
-        <v>6397700</v>
+        <v>6397661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124311630</v>
+        <v>124311342</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561506</v>
+        <v>561426</v>
       </c>
       <c r="R10" t="n">
-        <v>6397695</v>
+        <v>6397672</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124311750</v>
+        <v>124311630</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561517</v>
+        <v>561506</v>
       </c>
       <c r="R11" t="n">
-        <v>6397650</v>
+        <v>6397695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124311342</v>
+        <v>124311397</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561426</v>
+        <v>561425</v>
       </c>
       <c r="R12" t="n">
-        <v>6397672</v>
+        <v>6397700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124313772</v>
+        <v>124311311</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,38 +1911,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561604</v>
+        <v>561426</v>
       </c>
       <c r="R13" t="n">
-        <v>6397797</v>
+        <v>6397656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124313669</v>
+        <v>124311565</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2022,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561558</v>
+        <v>561474</v>
       </c>
       <c r="R14" t="n">
-        <v>6397704</v>
+        <v>6397726</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124313606</v>
+        <v>124313836</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561566</v>
+        <v>561563</v>
       </c>
       <c r="R15" t="n">
-        <v>6397691</v>
+        <v>6397866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124311500</v>
+        <v>124311718</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561472</v>
+        <v>561494</v>
       </c>
       <c r="R16" t="n">
-        <v>6397728</v>
+        <v>6397696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124313812</v>
+        <v>124311366</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561599</v>
+        <v>561431</v>
       </c>
       <c r="R17" t="n">
-        <v>6397835</v>
+        <v>6397666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124311285</v>
+        <v>124311790</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561408</v>
+        <v>561516</v>
       </c>
       <c r="R18" t="n">
-        <v>6397661</v>
+        <v>6397663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124358517</v>
+        <v>124359731</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,38 +2580,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561553</v>
+        <v>561466</v>
       </c>
       <c r="R19" t="n">
-        <v>6397632</v>
+        <v>6397610</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,14 +2672,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124370146</v>
+        <v>124370329</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2718,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561565</v>
+        <v>561575</v>
       </c>
       <c r="R20" t="n">
-        <v>6397707</v>
+        <v>6397630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370348</v>
+        <v>124370146</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2829,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561531</v>
+        <v>561565</v>
       </c>
       <c r="R21" t="n">
-        <v>6397636</v>
+        <v>6397707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2901,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124370329</v>
+        <v>124368692</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2925,28 +2934,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561575</v>
+        <v>561429</v>
       </c>
       <c r="R22" t="n">
-        <v>6397630</v>
+        <v>6397658</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,22 +3000,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369824</v>
+        <v>124369689</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,33 +3024,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3051,13 +3064,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561459</v>
+        <v>561476</v>
       </c>
       <c r="R23" t="n">
-        <v>6397783</v>
+        <v>6397662</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,17 +3094,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,17 +3119,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124370066</v>
+        <v>124358796</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,49 +3138,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561539</v>
+        <v>561533</v>
       </c>
       <c r="R24" t="n">
-        <v>6397729</v>
+        <v>6397592</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3210,29 +3219,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370019</v>
+        <v>124359633</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,49 +3249,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561503</v>
+        <v>561533</v>
       </c>
       <c r="R25" t="n">
-        <v>6397727</v>
+        <v>6397592</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3321,26 +3321,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124356739</v>
+        <v>124369964</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3374,19 +3373,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561558</v>
+        <v>561506</v>
       </c>
       <c r="R26" t="n">
-        <v>6397751</v>
+        <v>6397736</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3424,28 +3431,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124358796</v>
+        <v>124370066</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3454,50 +3462,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561533</v>
+        <v>561539</v>
       </c>
       <c r="R27" t="n">
-        <v>6397592</v>
+        <v>6397729</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,25 +3542,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370368</v>
+        <v>124370264</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3601,10 +3609,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561525</v>
+        <v>561577</v>
       </c>
       <c r="R28" t="n">
-        <v>6397602</v>
+        <v>6397687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,12 +3639,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3664,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124359731</v>
+        <v>124370348</v>
       </c>
       <c r="B29" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3676,50 +3684,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561466</v>
+        <v>561531</v>
       </c>
       <c r="R29" t="n">
-        <v>6397610</v>
+        <v>6397636</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,25 +3764,26 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370087</v>
+        <v>124370368</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3823,10 +3831,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561547</v>
+        <v>561525</v>
       </c>
       <c r="R30" t="n">
-        <v>6397746</v>
+        <v>6397602</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3886,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124359633</v>
+        <v>124369824</v>
       </c>
       <c r="B31" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3902,37 +3910,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561533</v>
+        <v>561459</v>
       </c>
       <c r="R31" t="n">
-        <v>6397592</v>
+        <v>6397783</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3962,6 +3978,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,19 +3997,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124369964</v>
+        <v>124358517</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4022,27 +4043,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561506</v>
+        <v>561553</v>
       </c>
       <c r="R32" t="n">
-        <v>6397736</v>
+        <v>6397632</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4080,26 +4093,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370108</v>
+        <v>124370087</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4147,10 +4159,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561549</v>
+        <v>561547</v>
       </c>
       <c r="R33" t="n">
-        <v>6397690</v>
+        <v>6397746</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4312,10 +4324,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124369689</v>
+        <v>124356739</v>
       </c>
       <c r="B35" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4324,53 +4336,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561476</v>
+        <v>561558</v>
       </c>
       <c r="R35" t="n">
-        <v>6397662</v>
+        <v>6397751</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4414,19 +4414,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124368692</v>
+        <v>124370108</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4459,28 +4459,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561429</v>
+        <v>561549</v>
       </c>
       <c r="R36" t="n">
-        <v>6397658</v>
+        <v>6397690</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4525,19 +4525,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370264</v>
+        <v>124370019</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561577</v>
+        <v>561503</v>
       </c>
       <c r="R37" t="n">
-        <v>6397687</v>
+        <v>6397727</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124359731</v>
+        <v>124369689</v>
       </c>
       <c r="B19" t="n">
-        <v>95705</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,50 +2580,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561466</v>
+        <v>561476</v>
       </c>
       <c r="R19" t="n">
-        <v>6397610</v>
+        <v>6397662</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2647,12 +2650,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,19 +2670,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124370329</v>
+        <v>124370348</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2727,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561575</v>
+        <v>561531</v>
       </c>
       <c r="R20" t="n">
-        <v>6397630</v>
+        <v>6397636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2793,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370146</v>
+        <v>124368692</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2823,28 +2826,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561565</v>
+        <v>561429</v>
       </c>
       <c r="R21" t="n">
-        <v>6397707</v>
+        <v>6397658</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,19 +2892,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124368692</v>
+        <v>124369964</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2934,28 +2937,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561429</v>
+        <v>561506</v>
       </c>
       <c r="R22" t="n">
-        <v>6397658</v>
+        <v>6397736</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,22 +3003,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369689</v>
+        <v>124370329</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,39 +3027,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3064,13 +3063,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561476</v>
+        <v>561575</v>
       </c>
       <c r="R23" t="n">
-        <v>6397662</v>
+        <v>6397630</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3094,12 +3093,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,6 +3107,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3119,17 +3119,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124358796</v>
+        <v>124358564</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3142,43 +3142,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561533</v>
+        <v>561553</v>
       </c>
       <c r="R24" t="n">
-        <v>6397592</v>
+        <v>6397632</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3230,17 +3221,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124359633</v>
+        <v>124370146</v>
       </c>
       <c r="B25" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3249,41 +3240,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561533</v>
+        <v>561565</v>
       </c>
       <c r="R25" t="n">
-        <v>6397592</v>
+        <v>6397707</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3321,25 +3320,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369964</v>
+        <v>124370019</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561506</v>
+        <v>561503</v>
       </c>
       <c r="R26" t="n">
-        <v>6397736</v>
+        <v>6397727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370066</v>
+        <v>124370087</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561539</v>
+        <v>561547</v>
       </c>
       <c r="R27" t="n">
-        <v>6397729</v>
+        <v>6397746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370264</v>
+        <v>124359731</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3573,49 +3573,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561577</v>
+        <v>561466</v>
       </c>
       <c r="R28" t="n">
-        <v>6397687</v>
+        <v>6397610</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3639,12 +3640,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3653,29 +3654,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370348</v>
+        <v>124369824</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3684,35 +3684,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561531</v>
+        <v>561459</v>
       </c>
       <c r="R29" t="n">
-        <v>6397636</v>
+        <v>6397783</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3758,13 +3758,17 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3776,14 +3780,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370368</v>
+        <v>124370264</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3831,10 +3835,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561525</v>
+        <v>561577</v>
       </c>
       <c r="R30" t="n">
-        <v>6397602</v>
+        <v>6397687</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,12 +3865,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3894,10 +3898,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124369824</v>
+        <v>124370108</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3906,35 +3910,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3942,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561459</v>
+        <v>561549</v>
       </c>
       <c r="R31" t="n">
-        <v>6397783</v>
+        <v>6397690</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3980,17 +3984,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4002,14 +4002,14 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124358517</v>
+        <v>124370066</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4043,19 +4043,27 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561553</v>
+        <v>561539</v>
       </c>
       <c r="R32" t="n">
-        <v>6397632</v>
+        <v>6397729</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4093,28 +4101,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370087</v>
+        <v>124358796</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4123,49 +4132,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561547</v>
+        <v>561533</v>
       </c>
       <c r="R33" t="n">
-        <v>6397746</v>
+        <v>6397592</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4203,29 +4213,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124358564</v>
+        <v>124358517</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4234,25 +4243,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4419,14 +4428,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370108</v>
+        <v>124370368</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4474,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561549</v>
+        <v>561525</v>
       </c>
       <c r="R36" t="n">
-        <v>6397690</v>
+        <v>6397602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4537,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124370019</v>
+        <v>124359633</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4549,49 +4558,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561503</v>
+        <v>561533</v>
       </c>
       <c r="R37" t="n">
-        <v>6397727</v>
+        <v>6397592</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4629,19 +4630,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 13978-2025 artfynd.xlsx
+++ b/artfynd/A 13978-2025 artfynd.xlsx
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124369689</v>
+        <v>124368692</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,53 +2580,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>knärot212321, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561476</v>
+        <v>561429</v>
       </c>
       <c r="R19" t="n">
-        <v>6397662</v>
+        <v>6397658</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2650,12 +2646,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,18 +2660,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2793,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124368692</v>
+        <v>124370368</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2826,28 +2823,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>knärot212321, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561429</v>
+        <v>561525</v>
       </c>
       <c r="R21" t="n">
-        <v>6397658</v>
+        <v>6397602</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2892,19 +2889,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124369964</v>
+        <v>124370264</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2952,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561506</v>
+        <v>561577</v>
       </c>
       <c r="R22" t="n">
-        <v>6397736</v>
+        <v>6397687</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2982,12 +2979,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,7 +3012,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124370329</v>
+        <v>124358517</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3049,27 +3046,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561575</v>
+        <v>561553</v>
       </c>
       <c r="R23" t="n">
-        <v>6397630</v>
+        <v>6397632</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3107,29 +3096,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124358564</v>
+        <v>124370108</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3138,41 +3126,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561553</v>
+        <v>561549</v>
       </c>
       <c r="R24" t="n">
-        <v>6397632</v>
+        <v>6397690</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3210,25 +3206,26 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370146</v>
+        <v>124370087</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3276,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561565</v>
+        <v>561547</v>
       </c>
       <c r="R25" t="n">
-        <v>6397707</v>
+        <v>6397746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,17 +3329,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370019</v>
+        <v>124359731</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3351,49 +3348,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561503</v>
+        <v>561466</v>
       </c>
       <c r="R26" t="n">
-        <v>6397727</v>
+        <v>6397610</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,29 +3429,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370087</v>
+        <v>124369689</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3462,35 +3459,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3498,13 +3499,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561547</v>
+        <v>561476</v>
       </c>
       <c r="R27" t="n">
-        <v>6397746</v>
+        <v>6397662</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3528,12 +3529,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,7 +3543,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124359731</v>
+        <v>124358564</v>
       </c>
       <c r="B28" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3573,47 +3573,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561466</v>
+        <v>561553</v>
       </c>
       <c r="R28" t="n">
-        <v>6397610</v>
+        <v>6397632</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3665,17 +3656,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124369824</v>
+        <v>124370329</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3684,35 +3675,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3720,10 +3711,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561459</v>
+        <v>561575</v>
       </c>
       <c r="R29" t="n">
-        <v>6397783</v>
+        <v>6397630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3758,17 +3749,13 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Stjärtfjäder av tupp</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3780,14 +3767,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370264</v>
+        <v>124370019</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3835,10 +3822,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561577</v>
+        <v>561503</v>
       </c>
       <c r="R30" t="n">
-        <v>6397687</v>
+        <v>6397727</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,12 +3852,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3898,10 +3885,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370108</v>
+        <v>124358796</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,49 +3897,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561549</v>
+        <v>561533</v>
       </c>
       <c r="R31" t="n">
-        <v>6397690</v>
+        <v>6397592</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3990,29 +3978,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sven Halling, Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370066</v>
+        <v>124359633</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>95705</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4021,49 +4008,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 13978, Stumpebo, Sm</t>
+          <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561539</v>
+        <v>561533</v>
       </c>
       <c r="R32" t="n">
-        <v>6397729</v>
+        <v>6397592</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4101,29 +4080,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
+          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124358796</v>
+        <v>124356739</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4132,47 +4110,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Söderskogen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561533</v>
+        <v>561558</v>
       </c>
       <c r="R33" t="n">
-        <v>6397592</v>
+        <v>6397751</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4224,14 +4193,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124358517</v>
+        <v>124370066</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4265,19 +4234,27 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561553</v>
+        <v>561539</v>
       </c>
       <c r="R34" t="n">
-        <v>6397632</v>
+        <v>6397729</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4315,28 +4292,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124356739</v>
+        <v>124369824</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4345,41 +4323,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561558</v>
+        <v>561459</v>
       </c>
       <c r="R35" t="n">
-        <v>6397751</v>
+        <v>6397783</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4409,6 +4395,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av tupp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4423,19 +4414,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling, Anna Drenk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124370368</v>
+        <v>124370146</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4483,10 +4474,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561525</v>
+        <v>561565</v>
       </c>
       <c r="R36" t="n">
-        <v>6397602</v>
+        <v>6397707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4546,10 +4537,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124359633</v>
+        <v>124369964</v>
       </c>
       <c r="B37" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4558,41 +4549,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderskogen, Sm</t>
+          <t>A 13978, Stumpebo, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561533</v>
+        <v>561506</v>
       </c>
       <c r="R37" t="n">
-        <v>6397592</v>
+        <v>6397736</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4630,18 +4629,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Drenk, Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk, Sven Halling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
